--- a/src/16-select-use-assess/Supporting_Data.xlsx
+++ b/src/16-select-use-assess/Supporting_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\user\MA103\src\16-select-use-assess\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0797E0E-4F69-40F8-9DE0-B5852B7035C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6824903-B2BE-4F9E-8E4B-A2DE9C7CCD23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="500" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Training Data" sheetId="1" r:id="rId1"/>
@@ -2987,6 +2987,31 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Residuals: Exponential Fit</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3047,6 +3072,69 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Exponential Fit'!$C$6:$C$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="18"/>
+                <c:pt idx="0">
+                  <c:v>17.82368704589862</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20.192536839019326</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>21.49253050287891</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>22.876217639210438</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>25.916571931926629</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>27.585078448421463</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>29.361003260935465</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>33.263215318484342</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>35.404698060269787</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>37.684049263941922</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>42.692432325929111</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>45.440967191108406</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>48.366452478025991</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>54.794575943811282</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>58.322245701638842</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>62.077026513908237</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>66.073539769408796</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>74.855016385916869</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
           <c:yVal>
             <c:numRef>
               <c:f>'Exponential Fit'!$D$6:$D$23</c:f>
@@ -3149,6 +3237,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -6220,6 +6309,36 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Residuals: Trigonometric</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Fit</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -6280,6 +6399,69 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Sinusoidal Fit'!$E$6:$E$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="18"/>
+                <c:pt idx="0">
+                  <c:v>21.911346094447559</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>21.049098477330816</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>21.171452990319079</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>21.66098536812741</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>23.712067479916008</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>25.249090277307914</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>27.104505788593034</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>31.681837567709717</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>34.351548778945961</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>37.235814560409416</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>43.515504427538154</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46.840072065154516</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>50.238257694972738</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>57.102060891942514</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>60.49042234316984</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>63.798735988923482</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>66.989727826713889</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>72.877471378477878</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
           <c:yVal>
             <c:numRef>
               <c:f>'Sinusoidal Fit'!$F$6:$F$23</c:f>
@@ -6382,6 +6564,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -10007,6 +10190,69 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Quadratic Fit'!$D$6:$D$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="18"/>
+                <c:pt idx="0">
+                  <c:v>19.508184243474528</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20.675113978381475</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>21.52517512828474</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>22.552967133154532</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>25.141743707793687</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>26.702728277563054</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>28.441443702298947</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>32.452067116670314</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>34.723975106305787</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>37.173613950907779</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>42.606084205011356</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>45.588915614512928</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>48.749477878981033</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>55.603794972816814</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>59.297549802184491</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>63.169035486518695</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>67.218252025819424</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>75.849877669320477</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
           <c:yVal>
             <c:numRef>
               <c:f>'Quadratic Fit'!$E$6:$E$23</c:f>
@@ -10109,6 +10355,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -13740,6 +13987,36 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Residuals:</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Polynomial Fit</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -13800,6 +14077,69 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Polynomial Fit'!$J$6:$J$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="18"/>
+                <c:pt idx="0">
+                  <c:v>22.209674582385869</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>21.522652427072966</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20.577053075439647</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20.658406141521688</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>23.48223190809572</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>25.573755641577307</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>27.780193697722105</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>32.286622767073162</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>34.681555222719595</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>37.273957278109549</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>43.159370652729592</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>46.385647297746345</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>49.719149298490947</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>56.638292364624704</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>60.332119523109213</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>64.259318210793936</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>68.245162336415888</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>72.194837574490521</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
           <c:yVal>
             <c:numRef>
               <c:f>'Polynomial Fit'!$K$6:$K$23</c:f>
@@ -13902,6 +14242,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
